--- a/employee_surveys/045_employee_career_growth_evaluation_form--employee_surveys.xlsx
+++ b/employee_surveys/045_employee_career_growth_evaluation_form--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>employee_career_growth_evaluation_form</t>
+          <t>Title of the Evaluation</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -538,17 +538,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>introduction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>current_job_title</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Current Job Title</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>years_of_service</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>employee_surveys</t>
+          <t>Years of Service</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>career_growth_goals</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>employee_career_growth_evaluation_form_helps_organizations_assess_employee_career_aspirations_and_development_needs_facilitating_meaningful_feedback_and_growth_opportunities</t>
+          <t>What are your top career growth goals?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>current_job_satisfaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>employee_surveys</t>
+          <t>How satisfied are you with your current job?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>career_satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>facilitating_meaningful_feedback_and_growth_opportunities</t>
+          <t>How satisfied are you with your career overall?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>job_description_match</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>employee_surveys</t>
+          <t>How well does your current job description match your career aspirations?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>job_fit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>How well does your current job fit with your skills and experience?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_title</t>
+          <t>job_growth_opportunities</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>employee_career_growth_evaluation_form</t>
+          <t>What growth opportunities do you have within your current role?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_description</t>
+          <t>career_development_areas</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>employee_career_growth_evaluation_form</t>
+          <t>Which areas of career development would you like to see more opportunities for?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_category</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>employee_surveys</t>
+          <t>Is there anything else you'd like to add or comment on?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="2" max="2"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -827,51 +827,306 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>career_growth_goals_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>employee_development_and_growth</t>
+          <t>professional_development_and_growth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Employee Development and Growth</t>
+          <t>Professional Development and Growth</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>career_growth_goals_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>career_development_and_growth</t>
+          <t>career_advancement_and_growth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Career Development and Growth</t>
+          <t>Career Advancement and Growth</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_title_choices</t>
+          <t>career_growth_goals_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>career_development_and_growth</t>
+          <t>leadership_development_and_growth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Career Development and Growth</t>
+          <t>Leadership Development and Growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>current_job_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>current_job_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>current_job_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>not_satisfied</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Not Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>career_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>career_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>career_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>not_satisfied</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Not Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>job_description_match_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>very_well</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Very Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>job_description_match_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>somewhat_well</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Somewhat Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>job_description_match_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>not_well</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Not Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>job_fit_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>very_well</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Very Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>job_fit_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>somewhat_well</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Somewhat Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>job_fit_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>not_well</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Not Well</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>career_development_areas_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>leadership_development</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Leadership Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>career_development_areas_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>professional_development</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Professional Development</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>career_development_areas_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>technical_development</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Technical Development</t>
         </is>
       </c>
     </row>
